--- a/AAII_Financials/Yearly/PMAX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PMAX_YR_FIN.xlsx
@@ -895,7 +895,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -973,7 +973,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7500</v>
+        <v>7600</v>
       </c>
       <c r="E17" s="3">
         <v>6800</v>
@@ -1006,7 +1006,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-1400</v>
+        <v>-1500</v>
       </c>
       <c r="E18" s="3">
         <v>-2100</v>
@@ -1087,7 +1087,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1000</v>
+        <v>-1100</v>
       </c>
       <c r="E21" s="3">
         <v>-1500</v>
@@ -1683,7 +1683,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
         <v>100</v>
@@ -1716,7 +1716,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1600</v>
+        <v>1400</v>
       </c>
       <c r="E43" s="3">
         <v>1000</v>
@@ -2142,7 +2142,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="E57" s="3">
         <v>900</v>
